--- a/sampleprojects/CorporateTax/excel/states/MS_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/MS_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <si>
     <t>DT: Determine MS Filing Requirement</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold ($250K gross receipts); result.ms_gross_receipts is greater than or equal to result.ms_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.ms_gross_receipts &gt;= result.ms_economic_nexus_threshold</t>
+    <t>ms_result.gross_receipts &gt;= ms_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.ms_has_nexus = true;</t>
+    <t>set ms_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.ms_has_nexus = false; set result.ms_tax_liability = 0.0;</t>
+    <t>set ms_result.has_nexus = false; set ms_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MS Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Mississippi nexus</t>
   </si>
   <si>
-    <t>result.ms_has_nexus is equal to true</t>
+    <t>ms_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Mississippi state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.ms_state_additions = 0.0; if result.ms_us_interest_income != 0.0 then set result.ms_state_additions = result.ms_state_additions + result.ms_us_interest_income; endif set result.ms_state_subtractions = 0.0; if result.ms_municipal_interest != 0.0 then set result.ms_state_subtractions = result.ms_state_subtractions + result.ms_municipal_interest; endif add (("Mississippi additions: $" + string value of (result.ms_state_additions)) + ", subtractions: $") + string value of (result.ms_state_subtractions) to job.audit_trail;</t>
+    <t>set ms_result.state_additions = 0.0; if ms_result.us_interest_income != 0.0 then set ms_result.state_additions = ms_result.state_additions + ms_result.us_interest_income; endif set ms_result.state_subtractions = 0.0; if ms_result.municipal_interest != 0.0 then set ms_result.state_subtractions = ms_result.state_subtractions + ms_result.municipal_interest; endif add (("Mississippi additions: $" + string value of (ms_result.state_additions)) + ", subtractions: $") + string value of (ms_result.state_subtractions) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.ms_state_additions = 0.0; set result.ms_state_subtractions = 0.0;</t>
+    <t>set ms_result.state_additions = 0.0; set ms_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MS State Tax</t>
@@ -145,19 +145,19 @@
     <t>Has positive taxable income; result.ms_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.ms_apportioned_income &gt; 0.0</t>
+    <t>ms_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Calculate Mississippi corporate tax (graduated rates 3%, 4%, 5%); Apply Mississippi graduated rates</t>
   </si>
   <si>
-    <t>set result.ms_taxable_income = the maximum of (result.ms_apportioned_income + result.ms_state_additions - result.ms_state_subtractions) and (0.0); set result.ms_tier1_tax = (the minimum of (result.ms_taxable_income) and (5000.0)) * result.ms_corp_tax_rate_tier1; set result.ms_tier2_tax = 0.0; set result.ms_tier3_tax = 0.0; if result.ms_taxable_income &gt; 5000.0 then set result.ms_tier2_tax = ((the minimum of (result.ms_taxable_income) and (10000.0)) - 5000.0) * result.ms_corp_tax_rate_tier2; endif if result.ms_taxable_income &gt; 10000.0 then set result.ms_tier3_tax = (result.ms_taxable_income - 10000.0) * result.ms_corp_tax_rate_tier3; endif set result.ms_tax_liability = the maximum of (result.ms_tier1_tax + result.ms_tier2_tax + result.ms_tier3_tax - result.ms_state_credits) and (0.0); set result.ms_refund_or_owed = result.ms_estimated_payments - result.ms_tax_liability; add "Mississippi taxable income: $" + string value of (result.ms_taxable_income) to job.audit_trail; add "Mississippi tax liability (graduated rates 3%-5%): $" + string value of (result.ms_tax_liability) to job.audit_trail;</t>
+    <t>set ms_result.taxable_income = the maximum of (ms_result.apportioned_income + ms_result.state_additions - ms_result.state_subtractions) and (0.0); set ms_result.tier1_tax = (the minimum of (ms_result.taxable_income) and (5000.0)) * ms_result.corp_tax_rate_tier1; set ms_result.tier2_tax = 0.0; set ms_result.tier3_tax = 0.0; if ms_result.taxable_income &gt; 5000.0 then set ms_result.tier2_tax = ((the minimum of (ms_result.taxable_income) and (10000.0)) - 5000.0) * ms_result.corp_tax_rate_tier2; endif if ms_result.taxable_income &gt; 10000.0 then set ms_result.tier3_tax = (ms_result.taxable_income - 10000.0) * ms_result.corp_tax_rate_tier3; endif set ms_result.tax_liability = the maximum of (ms_result.tier1_tax + ms_result.tier2_tax + ms_result.tier3_tax - ms_result.state_credits) and (0.0); set ms_result.refund_or_owed = ms_result.estimated_payments - ms_result.tax_liability; add "Mississippi taxable income: $" + string value of (ms_result.taxable_income) to job.audit_trail; add "Mississippi tax liability (graduated rates 3%-5%): $" + string value of (ms_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.ms_taxable_income = 0.0; set result.ms_tax_liability = 0.0;</t>
+    <t>set ms_result.taxable_income = 0.0; set ms_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -205,10 +205,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(13 attributes)</t>
+    <t>ms_apportionment</t>
+  </si>
+  <si>
+    <t>(9 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -226,37 +226,46 @@
     <t>MS uses single-sales factor apportionment (100% sales factor) for most businesses</t>
   </si>
   <si>
+    <t>bracket_tier1</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>5000.0</t>
+  </si>
+  <si>
+    <t>MS tier 1 bracket limit: $5,000</t>
+  </si>
+  <si>
+    <t>bracket_tier2</t>
+  </si>
+  <si>
+    <t>10000.0</t>
+  </si>
+  <si>
+    <t>MS tier 2 bracket limit: $10,000</t>
+  </si>
+  <si>
     <t>economic_nexus_threshold</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
     <t>250000.0</t>
   </si>
   <si>
     <t>MS economic nexus gross receipts threshold: $250,000</t>
   </si>
   <si>
-    <t>ms_bracket_tier1</t>
-  </si>
-  <si>
-    <t>5000.0</t>
-  </si>
-  <si>
-    <t>MS tier 1 bracket limit: $5,000</t>
-  </si>
-  <si>
-    <t>ms_bracket_tier2</t>
-  </si>
-  <si>
-    <t>10000.0</t>
-  </si>
-  <si>
-    <t>MS tier 2 bracket limit: $10,000</t>
-  </si>
-  <si>
-    <t>ms_tax_rate_tier1</t>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>MS top corporate income tax rate: 5% on income over $10,000 - MS Code § 27-7-5</t>
+  </si>
+  <si>
+    <t>tax_rate_tier1</t>
   </si>
   <si>
     <t>0.03</t>
@@ -265,7 +274,7 @@
     <t>MS tier 1 tax rate: 3% on first $5,000 of taxable income</t>
   </si>
   <si>
-    <t>ms_tax_rate_tier2</t>
+    <t>tax_rate_tier2</t>
   </si>
   <si>
     <t>0.04</t>
@@ -274,142 +283,103 @@
     <t>MS tier 2 tax rate: 4% on next $5,000 of taxable income ($5,001-$10,000)</t>
   </si>
   <si>
-    <t>ms_tax_rate_tier3</t>
-  </si>
-  <si>
-    <t>0.05</t>
+    <t>tax_rate_tier3</t>
   </si>
   <si>
     <t>MS tier 3 tax rate: 5% on taxable income over $10,000</t>
   </si>
   <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>MS does not have a separate transaction count threshold</t>
+  </si>
+  <si>
+    <t>ms_result</t>
+  </si>
+  <si>
+    <t>(19 attributes)</t>
+  </si>
+  <si>
+    <t>apportioned_income</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>Declared from decision-table usage; referenced by MS but never declared (campaign #948 Phase 1)</t>
+  </si>
+  <si>
+    <t>corp_tax_rate_tier1</t>
+  </si>
+  <si>
+    <t>corp_tax_rate_tier2</t>
+  </si>
+  <si>
+    <t>corp_tax_rate_tier3</t>
+  </si>
+  <si>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
     <t>state_additions</t>
   </si>
   <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>MS additions: federal interest income, IRC 199A addback, certain bonus depreciation, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Mississippi state code</t>
-  </si>
-  <si>
     <t>state_credits</t>
   </si>
   <si>
-    <t>MS tax credits: jobs creation, investment, research &amp; development, film production, etc.</t>
-  </si>
-  <si>
     <t>state_subtractions</t>
   </si>
   <si>
-    <t>MS subtractions: MS municipal bond interest, state income taxes, state NOL (5-year carryforward), etc.</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>MS top corporate income tax rate: 5% on income over $10,000 - MS Code § 27-7-5</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>MS does not have a separate transaction count threshold</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(19 attributes)</t>
-  </si>
-  <si>
-    <t>ms_apportioned_income</t>
-  </si>
-  <si>
-    <t>Declared from decision-table usage; referenced by MS but never declared (campaign #948 Phase 1)</t>
-  </si>
-  <si>
-    <t>ms_corp_tax_rate_tier1</t>
-  </si>
-  <si>
-    <t>ms_corp_tax_rate_tier2</t>
-  </si>
-  <si>
-    <t>ms_corp_tax_rate_tier3</t>
-  </si>
-  <si>
-    <t>ms_economic_nexus_threshold</t>
-  </si>
-  <si>
-    <t>ms_estimated_payments</t>
-  </si>
-  <si>
-    <t>ms_gross_receipts</t>
-  </si>
-  <si>
-    <t>ms_has_nexus</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>ms_municipal_interest</t>
-  </si>
-  <si>
-    <t>ms_refund_or_owed</t>
-  </si>
-  <si>
-    <t>ms_state_additions</t>
-  </si>
-  <si>
-    <t>ms_state_credits</t>
-  </si>
-  <si>
-    <t>ms_state_subtractions</t>
-  </si>
-  <si>
-    <t>ms_tax_liability</t>
-  </si>
-  <si>
-    <t>ms_taxable_income</t>
-  </si>
-  <si>
-    <t>ms_tier1_tax</t>
+    <t>tax_liability</t>
+  </si>
+  <si>
+    <t>taxable_income</t>
+  </si>
+  <si>
+    <t>tier1_tax</t>
   </si>
   <si>
     <t>Per-bracket tax; tax from bracket 1 (first $5,000). The original postfix held this in a fake local, which the EL authoring promoted to a real field (campaign #948).</t>
   </si>
   <si>
-    <t>ms_tier2_tax</t>
+    <t>tier2_tax</t>
   </si>
   <si>
     <t>Per-bracket tax; tax from bracket 2 ($5,001-$10,000). The original postfix held this in a fake local, which the EL authoring promoted to a real field (campaign #948).</t>
   </si>
   <si>
-    <t>ms_tier3_tax</t>
+    <t>tier3_tax</t>
   </si>
   <si>
     <t>Per-bracket tax; tax from bracket 3 (over $10,000). The original postfix held this in a fake local, which the EL authoring promoted to a real field (campaign #948).</t>
   </si>
   <si>
-    <t>ms_us_interest_income</t>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
@@ -2932,7 +2902,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
@@ -2941,7 +2911,7 @@
         <v>67</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -2964,10 +2934,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>91</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
@@ -3001,45 +2971,23 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="A13" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13" s="16" t="s">
+      <c r="B13" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
@@ -3055,7 +3003,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
@@ -3064,7 +3012,7 @@
         <v>67</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -3087,7 +3035,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>70</v>
@@ -3096,7 +3044,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
@@ -3105,7 +3053,7 @@
         <v>67</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -3131,13 +3079,13 @@
         <v>100</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
@@ -3146,7 +3094,7 @@
         <v>67</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -3165,30 +3113,52 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="A17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>70</v>
@@ -3197,7 +3167,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
@@ -3206,7 +3176,7 @@
         <v>67</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -3229,7 +3199,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>70</v>
@@ -3238,7 +3208,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
@@ -3247,7 +3217,7 @@
         <v>67</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -3270,7 +3240,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>70</v>
@@ -3279,7 +3249,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>8</v>
@@ -3288,7 +3258,7 @@
         <v>67</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>8</v>
@@ -3311,16 +3281,16 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>70</v>
+        <v>104</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>8</v>
@@ -3329,7 +3299,7 @@
         <v>67</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>8</v>
@@ -3352,7 +3322,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>70</v>
@@ -3361,7 +3331,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>8</v>
@@ -3370,7 +3340,7 @@
         <v>67</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>8</v>
@@ -3393,7 +3363,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>70</v>
@@ -3402,7 +3372,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>8</v>
@@ -3411,7 +3381,7 @@
         <v>67</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>8</v>
@@ -3434,7 +3404,7 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>70</v>
@@ -3443,7 +3413,7 @@
         <v>8</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>8</v>
@@ -3452,7 +3422,7 @@
         <v>67</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>8</v>
@@ -3475,16 +3445,16 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>8</v>
@@ -3493,7 +3463,7 @@
         <v>67</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I25" s="8" t="s">
         <v>8</v>
@@ -3516,7 +3486,7 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>70</v>
@@ -3525,7 +3495,7 @@
         <v>8</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>8</v>
@@ -3534,7 +3504,7 @@
         <v>67</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>8</v>
@@ -3557,7 +3527,7 @@
         <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>70</v>
@@ -3566,7 +3536,7 @@
         <v>8</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>8</v>
@@ -3575,7 +3545,7 @@
         <v>67</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>8</v>
@@ -3598,7 +3568,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>70</v>
@@ -3607,7 +3577,7 @@
         <v>8</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>8</v>
@@ -3616,7 +3586,7 @@
         <v>67</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>8</v>
@@ -3639,7 +3609,7 @@
         <v>8</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>70</v>
@@ -3648,7 +3618,7 @@
         <v>8</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>8</v>
@@ -3657,7 +3627,7 @@
         <v>67</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I29" s="8" t="s">
         <v>8</v>
@@ -3680,7 +3650,7 @@
         <v>8</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>70</v>
@@ -3689,7 +3659,7 @@
         <v>8</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>8</v>
@@ -3698,7 +3668,7 @@
         <v>67</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>8</v>
@@ -3721,7 +3691,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>70</v>
@@ -3730,7 +3700,7 @@
         <v>8</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>8</v>
@@ -3739,7 +3709,7 @@
         <v>67</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>8</v>
@@ -3762,7 +3732,7 @@
         <v>8</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>70</v>
@@ -3771,7 +3741,7 @@
         <v>8</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>8</v>
@@ -3780,7 +3750,7 @@
         <v>67</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>8</v>
@@ -3795,170 +3765,6 @@
         <v>8</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H33" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M33" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H34" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M34" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H35" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M35" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M36" s="7" t="s">
         <v>8</v>
       </c>
     </row>
